--- a/Parbaudes_lapu_versijas_jautajumi.xlsx
+++ b/Parbaudes_lapu_versijas_jautajumi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\vpp-cfla\cfla_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\vpp-cfla\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD0ED7EB-B52E-4CC7-BA84-87B760630EB9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5591662D-27A4-4780-94BF-1B599817B36F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="209">
   <si>
     <t>09.12.2019.</t>
   </si>
@@ -307,6 +307,351 @@
   </si>
   <si>
     <t>nosacījums</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>33.1</t>
+  </si>
+  <si>
+    <t>33.2</t>
+  </si>
+  <si>
+    <t>33.3</t>
+  </si>
+  <si>
+    <t>33.4</t>
+  </si>
+  <si>
+    <t>33.5</t>
+  </si>
+  <si>
+    <t>33.6</t>
+  </si>
+  <si>
+    <t>33.7</t>
+  </si>
+  <si>
+    <t>33.8</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>35.1</t>
+  </si>
+  <si>
+    <t>35.2</t>
+  </si>
+  <si>
+    <t>35.3</t>
+  </si>
+  <si>
+    <t>35.4</t>
+  </si>
+  <si>
+    <t>35.5</t>
+  </si>
+  <si>
+    <t>35.6</t>
+  </si>
+  <si>
+    <t>35.7</t>
+  </si>
+  <si>
+    <t>35.8</t>
+  </si>
+  <si>
+    <t>35.9</t>
+  </si>
+  <si>
+    <t>35.10</t>
+  </si>
+  <si>
+    <t>35.11</t>
+  </si>
+  <si>
+    <t>35.12</t>
+  </si>
+  <si>
+    <t>35.13</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>36.1</t>
+  </si>
+  <si>
+    <t>36.2</t>
+  </si>
+  <si>
+    <t>36.3</t>
+  </si>
+  <si>
+    <t>36.4</t>
+  </si>
+  <si>
+    <t>36.5</t>
+  </si>
+  <si>
+    <t>36.6</t>
+  </si>
+  <si>
+    <t>36.7</t>
+  </si>
+  <si>
+    <t>36.8</t>
+  </si>
+  <si>
+    <t>36.9</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>37.1</t>
+  </si>
+  <si>
+    <t>37.2</t>
+  </si>
+  <si>
+    <t>37.3</t>
+  </si>
+  <si>
+    <t>37.4</t>
+  </si>
+  <si>
+    <t>37.5</t>
+  </si>
+  <si>
+    <t>37.6</t>
+  </si>
+  <si>
+    <t>37.7</t>
+  </si>
+  <si>
+    <t>37.8</t>
+  </si>
+  <si>
+    <t>37.9</t>
+  </si>
+  <si>
+    <t>37.11</t>
+  </si>
+  <si>
+    <t>37.12</t>
+  </si>
+  <si>
+    <t>37.13</t>
+  </si>
+  <si>
+    <t>37.14</t>
+  </si>
+  <si>
+    <t>37.15</t>
+  </si>
+  <si>
+    <t>37.16</t>
+  </si>
+  <si>
+    <t>37.17</t>
+  </si>
+  <si>
+    <t>37.18</t>
+  </si>
+  <si>
+    <t>37.19</t>
+  </si>
+  <si>
+    <t>37.20</t>
+  </si>
+  <si>
+    <t>37.21</t>
+  </si>
+  <si>
+    <t>37.22</t>
+  </si>
+  <si>
+    <t>37.23</t>
+  </si>
+  <si>
+    <t>37.24</t>
+  </si>
+  <si>
+    <t>37.25</t>
+  </si>
+  <si>
+    <t>37.26</t>
+  </si>
+  <si>
+    <t>37.27</t>
+  </si>
+  <si>
+    <t>37.28</t>
+  </si>
+  <si>
+    <t>37.29</t>
+  </si>
+  <si>
+    <t>37.30</t>
+  </si>
+  <si>
+    <t>37.31</t>
+  </si>
+  <si>
+    <t>37.32</t>
+  </si>
+  <si>
+    <t>37.33</t>
+  </si>
+  <si>
+    <t>37.34</t>
+  </si>
+  <si>
+    <t>37.35</t>
+  </si>
+  <si>
+    <t>37.36</t>
+  </si>
+  <si>
+    <t>37.37</t>
+  </si>
+  <si>
+    <t>37.38</t>
+  </si>
+  <si>
+    <t>37.39</t>
+  </si>
+  <si>
+    <t>37.40</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>38.1</t>
+  </si>
+  <si>
+    <t>38.2</t>
+  </si>
+  <si>
+    <t>38.3</t>
+  </si>
+  <si>
+    <t>38.4</t>
+  </si>
+  <si>
+    <t>38.5</t>
+  </si>
+  <si>
+    <t>38.7</t>
+  </si>
+  <si>
+    <t>38.8</t>
+  </si>
+  <si>
+    <t>38.9</t>
+  </si>
+  <si>
+    <t>38.10</t>
+  </si>
+  <si>
+    <t>38.11</t>
+  </si>
+  <si>
+    <t>38.12</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49.1</t>
+  </si>
+  <si>
+    <t>49.2</t>
+  </si>
+  <si>
+    <t>49.3</t>
+  </si>
+  <si>
+    <t>49.4</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>66</t>
   </si>
 </sst>
 </file>
@@ -640,10 +985,10 @@
   <cols>
     <col min="1" max="1" width="11.42578125" style="2" customWidth="1"/>
     <col min="2" max="2" width="13" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="22.140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -653,16 +998,16 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -715,6 +1060,9 @@
       <c r="B8" s="2">
         <v>8</v>
       </c>
+      <c r="C8" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -723,6 +1071,9 @@
       <c r="B9" s="2">
         <v>9</v>
       </c>
+      <c r="C9" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -731,6 +1082,9 @@
       <c r="B10" s="2">
         <v>10</v>
       </c>
+      <c r="C10" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -739,6 +1093,9 @@
       <c r="B11" s="2">
         <v>10.1</v>
       </c>
+      <c r="C11" s="2">
+        <v>8.1</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -747,6 +1104,9 @@
       <c r="B12" s="2">
         <v>10.199999999999999</v>
       </c>
+      <c r="C12" s="2">
+        <v>8.1999999999999993</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -755,6 +1115,9 @@
       <c r="B13" s="2">
         <v>10.3</v>
       </c>
+      <c r="C13" s="2">
+        <v>8.3000000000000007</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -763,6 +1126,9 @@
       <c r="B14" s="2">
         <v>11</v>
       </c>
+      <c r="C14" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -771,6 +1137,9 @@
       <c r="B15" s="2">
         <v>12</v>
       </c>
+      <c r="C15" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -779,1120 +1148,1549 @@
       <c r="B16" s="2">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C16" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C17" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C18" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>15</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C19" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>16</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C20" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C21" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>19</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C23" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C24" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>21</v>
       </c>
       <c r="B25" s="2">
         <v>22</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C25" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>22</v>
       </c>
       <c r="B26" s="2">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C26" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>23</v>
       </c>
       <c r="B27" s="2">
         <v>24</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C27" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>24</v>
       </c>
       <c r="B28" s="2">
         <v>25</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C28" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>25</v>
       </c>
       <c r="B29" s="2">
         <v>26</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C29" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>26</v>
       </c>
       <c r="B30" s="2">
         <v>27</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C30" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>27</v>
       </c>
       <c r="B31" s="2">
         <v>28</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C31" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>28</v>
       </c>
       <c r="B32" s="2">
         <v>29</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C32" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>29</v>
       </c>
       <c r="B33" s="2">
         <v>30</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C33" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>30</v>
       </c>
       <c r="B34" s="2">
         <v>31</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C34" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>31</v>
       </c>
       <c r="B35" s="2">
         <v>33</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C35" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>32</v>
       </c>
       <c r="B36" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C36" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>33</v>
       </c>
       <c r="B37" s="2">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C37" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>34</v>
       </c>
       <c r="B38" s="2">
         <v>37</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C38" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>35</v>
       </c>
       <c r="B39" s="2">
         <v>38</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C39" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>35.1</v>
       </c>
       <c r="B40" s="2">
         <v>38.1</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C40" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>35.200000000000003</v>
       </c>
       <c r="B41" s="2">
         <v>38.200000000000003</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C41" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>35.299999999999997</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C42" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>35.4</v>
       </c>
       <c r="B43" s="2">
         <v>38.5</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C43" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>35.5</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C44" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>35.6</v>
       </c>
       <c r="B45" s="2">
         <v>38.700000000000003</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C45" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>35.700000000000003</v>
       </c>
       <c r="B46" s="2">
         <v>38.799999999999997</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C46" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>35.799999999999997</v>
       </c>
       <c r="B47" s="2">
         <v>38.9</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C47" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>36</v>
       </c>
       <c r="B48" s="2">
         <v>39</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C48" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>37</v>
       </c>
       <c r="B49" s="2">
         <v>40</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C49" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>37.1</v>
       </c>
       <c r="B50" s="2">
         <v>40.1</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C50" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>37.200000000000003</v>
       </c>
       <c r="B51" s="2">
         <v>40.200000000000003</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C51" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>37.299999999999997</v>
       </c>
       <c r="B52" s="2">
         <v>40.299999999999997</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C52" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>37.4</v>
       </c>
       <c r="B53" s="2">
         <v>40.4</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C53" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>37.5</v>
       </c>
       <c r="B54" s="2">
         <v>40.5</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C54" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>37.6</v>
       </c>
       <c r="B55" s="2">
         <v>40.6</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C55" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>37.700000000000003</v>
       </c>
       <c r="B56" s="2">
         <v>40.700000000000003</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C56" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>37.799999999999997</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C57" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>37.9</v>
       </c>
       <c r="B58" s="2">
         <v>40.11</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C58" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B59" s="2">
         <v>40.119999999999997</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C59" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>37.11</v>
       </c>
       <c r="B60" s="2">
         <v>40.130000000000003</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C60" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>37.119999999999997</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C61" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>37.130000000000003</v>
       </c>
       <c r="B62" s="2">
         <v>40.14</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C62" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>38</v>
       </c>
       <c r="B63" s="2">
         <v>41</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C63" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>38.1</v>
       </c>
       <c r="B64" s="2">
         <v>41.1</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C64" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>38.200000000000003</v>
       </c>
       <c r="B65" s="2">
         <v>41.2</v>
       </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C65" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>38.299999999999997</v>
       </c>
       <c r="B66" s="2">
         <v>41.3</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C66" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>38.4</v>
       </c>
       <c r="B67" s="2">
         <v>41.4</v>
       </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C67" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>38.5</v>
       </c>
       <c r="B68" s="2">
         <v>41.5</v>
       </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C68" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>38.6</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C69" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>38.700000000000003</v>
       </c>
       <c r="B70" s="2">
         <v>41.8</v>
       </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C70" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>38.799999999999997</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C71" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>38.9</v>
       </c>
       <c r="B72" s="2">
         <v>41.11</v>
       </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C72" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>39</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C73" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>39.1</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C74" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>39.200000000000003</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C75" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>39.299999999999997</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C76" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>39.4</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C77" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>39.5</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C78" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>39.6</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C79" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>39.700000000000003</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C80" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>39.799999999999997</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C81" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>39.9</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C82" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C83" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>39.11</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C84" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>39.119999999999997</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C85" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>39.130000000000003</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C86" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>39.14</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C87" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>39.15</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C88" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>39.159999999999997</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C89" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>39.17</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C90" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>39.18</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C91" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>39.19</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C92" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C93" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>39.21</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C94" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>39.22</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C95" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>39.229999999999997</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C96" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>39.24</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C97" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>39.25</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C98" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>39.26</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C99" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>39.270000000000003</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C100" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>39.28</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C101" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>39.29</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C102" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C103" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>39.31</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C104" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>39.32</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C105" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>39.33</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C106" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>39.340000000000003</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C107" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>39.35</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C108" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>39.36</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C109" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>39.369999999999997</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C110" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>39.380000000000003</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C111" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>39.39</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C112" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C113" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>40</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C114" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>40.1</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C115" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>40.200000000000003</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C116" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>40.299999999999997</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C117" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>40.4</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C118" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>40.5</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C119" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>40.6</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C120" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>40.700000000000003</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C121" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>40.799999999999997</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C122" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>40.9</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C123" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C124" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>40.11</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C125" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>40.119999999999997</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C126" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>41</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C127" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>42</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C128" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>43</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C129" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>44</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C130" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>45</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C131" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>46</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C132" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>47</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C133" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>48</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C134" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>49</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C135" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>50</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C136" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>51</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C137" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>51.1</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C138" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>51.2</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C139" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>51.3</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C140" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>51.4</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C141" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>52</v>
       </c>
       <c r="B142" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C142" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>53</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C143" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>54</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C144" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C145" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>56</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C146" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>57</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C147" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>58</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C148" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>59</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C149" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>60</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C150" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>61</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C151" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>62</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C152" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>63</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C153" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>64</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C154" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>65</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C155" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>66</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C156" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>67</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C157" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>68</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>67</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/Parbaudes_lapu_versijas_jautajumi.xlsx
+++ b/Parbaudes_lapu_versijas_jautajumi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\vpp-cfla\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5591662D-27A4-4780-94BF-1B599817B36F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506534F9-9A42-40BD-88EC-ACB1C0D9F703}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="210">
   <si>
     <t>09.12.2019.</t>
   </si>
@@ -652,6 +652,9 @@
   </si>
   <si>
     <t>66</t>
+  </si>
+  <si>
+    <t>7</t>
   </si>
 </sst>
 </file>
@@ -988,7 +991,7 @@
     <col min="3" max="3" width="12.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="15.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="17.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="22.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1063,6 +1066,9 @@
       <c r="C8" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="D8" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -1074,6 +1080,9 @@
       <c r="C9" s="2">
         <v>7</v>
       </c>
+      <c r="D9" s="2" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -1085,6 +1094,9 @@
       <c r="C10" s="2">
         <v>8</v>
       </c>
+      <c r="D10" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -1096,6 +1108,9 @@
       <c r="C11" s="2">
         <v>8.1</v>
       </c>
+      <c r="D11" s="2">
+        <v>8.1</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -1107,6 +1122,9 @@
       <c r="C12" s="2">
         <v>8.1999999999999993</v>
       </c>
+      <c r="D12" s="2">
+        <v>8.1999999999999993</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -1118,6 +1136,9 @@
       <c r="C13" s="2">
         <v>8.3000000000000007</v>
       </c>
+      <c r="D13" s="2">
+        <v>8.3000000000000007</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1129,6 +1150,9 @@
       <c r="C14" s="2">
         <v>9</v>
       </c>
+      <c r="D14" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1140,6 +1164,9 @@
       <c r="C15" s="2">
         <v>10</v>
       </c>
+      <c r="D15" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1151,8 +1178,11 @@
       <c r="C16" s="2">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>13</v>
       </c>
@@ -1162,64 +1192,88 @@
       <c r="C17" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>14</v>
       </c>
       <c r="C18" s="2">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>15</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>17</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>18</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>20</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>21</v>
       </c>
@@ -1229,8 +1283,11 @@
       <c r="C25" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D25" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>22</v>
       </c>
@@ -1240,8 +1297,11 @@
       <c r="C26" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D26" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>23</v>
       </c>
@@ -1251,8 +1311,11 @@
       <c r="C27" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D27" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>24</v>
       </c>
@@ -1262,8 +1325,11 @@
       <c r="C28" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D28" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>25</v>
       </c>
@@ -1273,8 +1339,11 @@
       <c r="C29" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D29" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>26</v>
       </c>
@@ -1284,8 +1353,11 @@
       <c r="C30" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D30" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>27</v>
       </c>
@@ -1295,8 +1367,11 @@
       <c r="C31" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D31" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>28</v>
       </c>
@@ -1306,8 +1381,11 @@
       <c r="C32" s="2" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D32" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>29</v>
       </c>
@@ -1317,8 +1395,11 @@
       <c r="C33" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D33" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>30</v>
       </c>
@@ -1328,8 +1409,11 @@
       <c r="C34" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D34" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>31</v>
       </c>
@@ -1339,8 +1423,11 @@
       <c r="C35" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D35" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>32</v>
       </c>
@@ -1350,8 +1437,11 @@
       <c r="C36" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D36" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>33</v>
       </c>
@@ -1361,8 +1451,11 @@
       <c r="C37" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D37" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>34</v>
       </c>
@@ -1372,8 +1465,11 @@
       <c r="C38" s="2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D38" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>35</v>
       </c>
@@ -1383,8 +1479,11 @@
       <c r="C39" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D39" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>35.1</v>
       </c>
@@ -1394,8 +1493,11 @@
       <c r="C40" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D40" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>35.200000000000003</v>
       </c>
@@ -1405,8 +1507,11 @@
       <c r="C41" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D41" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>35.299999999999997</v>
       </c>
@@ -1416,8 +1521,11 @@
       <c r="C42" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D42" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>35.4</v>
       </c>
@@ -1427,8 +1535,11 @@
       <c r="C43" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D43" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>35.5</v>
       </c>
@@ -1438,8 +1549,11 @@
       <c r="C44" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D44" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>35.6</v>
       </c>
@@ -1449,8 +1563,11 @@
       <c r="C45" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D45" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>35.700000000000003</v>
       </c>
@@ -1460,8 +1577,11 @@
       <c r="C46" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D46" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>35.799999999999997</v>
       </c>
@@ -1471,8 +1591,11 @@
       <c r="C47" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D47" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>36</v>
       </c>
@@ -1482,8 +1605,11 @@
       <c r="C48" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D48" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>37</v>
       </c>
@@ -1493,8 +1619,11 @@
       <c r="C49" s="2" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D49" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>37.1</v>
       </c>
@@ -1504,8 +1633,11 @@
       <c r="C50" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D50" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>37.200000000000003</v>
       </c>
@@ -1515,8 +1647,11 @@
       <c r="C51" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D51" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>37.299999999999997</v>
       </c>
@@ -1526,8 +1661,11 @@
       <c r="C52" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D52" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>37.4</v>
       </c>
@@ -1537,8 +1675,11 @@
       <c r="C53" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D53" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>37.5</v>
       </c>
@@ -1548,8 +1689,11 @@
       <c r="C54" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D54" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>37.6</v>
       </c>
@@ -1559,8 +1703,11 @@
       <c r="C55" s="2" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D55" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>37.700000000000003</v>
       </c>
@@ -1570,8 +1717,11 @@
       <c r="C56" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D56" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>37.799999999999997</v>
       </c>
@@ -1581,8 +1731,11 @@
       <c r="C57" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D57" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>37.9</v>
       </c>
@@ -1592,8 +1745,11 @@
       <c r="C58" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D58" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>7</v>
       </c>
@@ -1603,8 +1759,11 @@
       <c r="C59" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D59" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>37.11</v>
       </c>
@@ -1614,8 +1773,11 @@
       <c r="C60" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D60" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>37.119999999999997</v>
       </c>
@@ -1625,8 +1787,11 @@
       <c r="C61" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D61" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>37.130000000000003</v>
       </c>
@@ -1636,8 +1801,11 @@
       <c r="C62" s="2" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D62" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>38</v>
       </c>
@@ -1647,8 +1815,11 @@
       <c r="C63" s="2" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D63" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>38.1</v>
       </c>
@@ -1658,8 +1829,11 @@
       <c r="C64" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D64" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>38.200000000000003</v>
       </c>
@@ -1669,8 +1843,11 @@
       <c r="C65" s="2" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D65" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>38.299999999999997</v>
       </c>
@@ -1680,8 +1857,11 @@
       <c r="C66" s="2" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D66" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>38.4</v>
       </c>
@@ -1691,8 +1871,11 @@
       <c r="C67" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D67" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>38.5</v>
       </c>
@@ -1702,8 +1885,11 @@
       <c r="C68" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D68" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>38.6</v>
       </c>
@@ -1713,8 +1899,11 @@
       <c r="C69" s="2" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D69" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>38.700000000000003</v>
       </c>
@@ -1724,8 +1913,11 @@
       <c r="C70" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D70" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>38.799999999999997</v>
       </c>
@@ -1735,8 +1927,11 @@
       <c r="C71" s="2" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D71" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>38.9</v>
       </c>
@@ -1746,8 +1941,11 @@
       <c r="C72" s="2" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D72" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>39</v>
       </c>
@@ -1757,8 +1955,11 @@
       <c r="C73" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D73" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>39.1</v>
       </c>
@@ -1768,8 +1969,11 @@
       <c r="C74" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D74" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>39.200000000000003</v>
       </c>
@@ -1779,8 +1983,11 @@
       <c r="C75" s="2" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D75" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>39.299999999999997</v>
       </c>
@@ -1790,8 +1997,11 @@
       <c r="C76" s="2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D76" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>39.4</v>
       </c>
@@ -1801,8 +2011,11 @@
       <c r="C77" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D77" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>39.5</v>
       </c>
@@ -1812,8 +2025,11 @@
       <c r="C78" s="2" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D78" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>39.6</v>
       </c>
@@ -1823,8 +2039,11 @@
       <c r="C79" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D79" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>39.700000000000003</v>
       </c>
@@ -1834,8 +2053,11 @@
       <c r="C80" s="2" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D80" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>39.799999999999997</v>
       </c>
@@ -1845,8 +2067,11 @@
       <c r="C81" s="2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D81" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>39.9</v>
       </c>
@@ -1856,8 +2081,11 @@
       <c r="C82" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D82" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>8</v>
       </c>
@@ -1867,8 +2095,11 @@
       <c r="C83" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D83" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>39.11</v>
       </c>
@@ -1878,8 +2109,11 @@
       <c r="C84" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D84" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>39.119999999999997</v>
       </c>
@@ -1889,8 +2123,11 @@
       <c r="C85" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D85" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>39.130000000000003</v>
       </c>
@@ -1900,8 +2137,11 @@
       <c r="C86" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D86" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>39.14</v>
       </c>
@@ -1911,8 +2151,11 @@
       <c r="C87" s="2" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D87" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>39.15</v>
       </c>
@@ -1922,8 +2165,11 @@
       <c r="C88" s="2" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D88" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>39.159999999999997</v>
       </c>
@@ -1933,8 +2179,11 @@
       <c r="C89" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D89" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>39.17</v>
       </c>
@@ -1944,8 +2193,11 @@
       <c r="C90" s="2" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D90" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>39.18</v>
       </c>
@@ -1955,8 +2207,11 @@
       <c r="C91" s="2" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D91" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>39.19</v>
       </c>
@@ -1966,8 +2221,11 @@
       <c r="C92" s="2" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D92" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>9</v>
       </c>
@@ -1977,8 +2235,11 @@
       <c r="C93" s="2" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D93" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>39.21</v>
       </c>
@@ -1988,8 +2249,11 @@
       <c r="C94" s="2" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D94" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>39.22</v>
       </c>
@@ -1999,8 +2263,11 @@
       <c r="C95" s="2" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D95" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>39.229999999999997</v>
       </c>
@@ -2010,8 +2277,11 @@
       <c r="C96" s="2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D96" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>39.24</v>
       </c>
@@ -2021,8 +2291,11 @@
       <c r="C97" s="2" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D97" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>39.25</v>
       </c>
@@ -2032,8 +2305,11 @@
       <c r="C98" s="2" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D98" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>39.26</v>
       </c>
@@ -2043,8 +2319,11 @@
       <c r="C99" s="2" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D99" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>39.270000000000003</v>
       </c>
@@ -2054,8 +2333,11 @@
       <c r="C100" s="2" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D100" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>39.28</v>
       </c>
@@ -2065,8 +2347,11 @@
       <c r="C101" s="2" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D101" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>39.29</v>
       </c>
@@ -2076,8 +2361,11 @@
       <c r="C102" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D102" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>11</v>
       </c>
@@ -2087,8 +2375,11 @@
       <c r="C103" s="2" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D103" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>39.31</v>
       </c>
@@ -2098,8 +2389,11 @@
       <c r="C104" s="2" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D104" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>39.32</v>
       </c>
@@ -2109,8 +2403,11 @@
       <c r="C105" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D105" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>39.33</v>
       </c>
@@ -2120,8 +2417,11 @@
       <c r="C106" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D106" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>39.340000000000003</v>
       </c>
@@ -2131,8 +2431,11 @@
       <c r="C107" s="2" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D107" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>39.35</v>
       </c>
@@ -2142,8 +2445,11 @@
       <c r="C108" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D108" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>39.36</v>
       </c>
@@ -2153,8 +2459,11 @@
       <c r="C109" s="2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D109" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>39.369999999999997</v>
       </c>
@@ -2164,8 +2473,11 @@
       <c r="C110" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D110" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>39.380000000000003</v>
       </c>
@@ -2175,8 +2487,11 @@
       <c r="C111" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D111" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>39.39</v>
       </c>
@@ -2186,8 +2501,11 @@
       <c r="C112" s="2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D112" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>22</v>
       </c>
@@ -2197,8 +2515,11 @@
       <c r="C113" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D113" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>40</v>
       </c>
@@ -2208,8 +2529,11 @@
       <c r="C114" s="2" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D114" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>40.1</v>
       </c>
@@ -2219,8 +2543,11 @@
       <c r="C115" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D115" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>40.200000000000003</v>
       </c>
@@ -2230,8 +2557,11 @@
       <c r="C116" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D116" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>40.299999999999997</v>
       </c>
@@ -2241,8 +2571,11 @@
       <c r="C117" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D117" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>40.4</v>
       </c>
@@ -2252,8 +2585,11 @@
       <c r="C118" s="2" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D118" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>40.5</v>
       </c>
@@ -2263,8 +2599,11 @@
       <c r="C119" s="2" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D119" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>40.6</v>
       </c>
@@ -2274,8 +2613,11 @@
       <c r="C120" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D120" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>40.700000000000003</v>
       </c>
@@ -2285,8 +2627,11 @@
       <c r="C121" s="2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D121" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>40.799999999999997</v>
       </c>
@@ -2296,8 +2641,11 @@
       <c r="C122" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D122" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>40.9</v>
       </c>
@@ -2307,8 +2655,11 @@
       <c r="C123" s="2" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D123" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>54</v>
       </c>
@@ -2318,8 +2669,11 @@
       <c r="C124" s="2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D124" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>40.11</v>
       </c>
@@ -2329,8 +2683,11 @@
       <c r="C125" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D125" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>40.119999999999997</v>
       </c>
@@ -2340,8 +2697,11 @@
       <c r="C126" s="2" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D126" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>41</v>
       </c>
@@ -2351,8 +2711,11 @@
       <c r="C127" s="2" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D127" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>42</v>
       </c>
@@ -2362,8 +2725,11 @@
       <c r="C128" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D128" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>43</v>
       </c>
@@ -2373,8 +2739,11 @@
       <c r="C129" s="2" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D129" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>44</v>
       </c>
@@ -2384,8 +2753,11 @@
       <c r="C130" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D130" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>45</v>
       </c>
@@ -2395,8 +2767,11 @@
       <c r="C131" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D131" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>46</v>
       </c>
@@ -2406,8 +2781,11 @@
       <c r="C132" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D132" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>47</v>
       </c>
@@ -2417,8 +2795,11 @@
       <c r="C133" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D133" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>48</v>
       </c>
@@ -2428,8 +2809,11 @@
       <c r="C134" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D134" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>49</v>
       </c>
@@ -2439,8 +2823,11 @@
       <c r="C135" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D135" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>50</v>
       </c>
@@ -2450,8 +2837,11 @@
       <c r="C136" s="2" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D136" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>51</v>
       </c>
@@ -2461,8 +2851,11 @@
       <c r="C137" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D137" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>51.1</v>
       </c>
@@ -2472,8 +2865,11 @@
       <c r="C138" s="2" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D138" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>51.2</v>
       </c>
@@ -2483,8 +2879,11 @@
       <c r="C139" s="2" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D139" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>51.3</v>
       </c>
@@ -2494,8 +2893,11 @@
       <c r="C140" s="2" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D140" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>51.4</v>
       </c>
@@ -2505,8 +2907,11 @@
       <c r="C141" s="2" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D141" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>52</v>
       </c>
@@ -2516,8 +2921,11 @@
       <c r="C142" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D142" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>53</v>
       </c>
@@ -2527,8 +2935,11 @@
       <c r="C143" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D143" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>54</v>
       </c>
@@ -2538,8 +2949,11 @@
       <c r="C144" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D144" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>55</v>
       </c>
@@ -2549,8 +2963,11 @@
       <c r="C145" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D145" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>56</v>
       </c>
@@ -2560,8 +2977,11 @@
       <c r="C146" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D146" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>57</v>
       </c>
@@ -2571,8 +2991,11 @@
       <c r="C147" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D147" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>58</v>
       </c>
@@ -2582,8 +3005,11 @@
       <c r="C148" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D148" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>59</v>
       </c>
@@ -2593,8 +3019,11 @@
       <c r="C149" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D149" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>60</v>
       </c>
@@ -2604,8 +3033,11 @@
       <c r="C150" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D150" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>61</v>
       </c>
@@ -2615,8 +3047,11 @@
       <c r="C151" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D151" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>62</v>
       </c>
@@ -2626,8 +3061,11 @@
       <c r="C152" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D152" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>63</v>
       </c>
@@ -2637,8 +3075,11 @@
       <c r="C153" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D153" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>64</v>
       </c>
@@ -2648,8 +3089,11 @@
       <c r="C154" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D154" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>65</v>
       </c>
@@ -2659,8 +3103,11 @@
       <c r="C155" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D155" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>66</v>
       </c>
@@ -2670,8 +3117,11 @@
       <c r="C156" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D156" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>67</v>
       </c>
@@ -2681,8 +3131,11 @@
       <c r="C157" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D157" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>68</v>
       </c>
@@ -2690,6 +3143,9 @@
         <v>67</v>
       </c>
       <c r="C158" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D158" s="2" t="s">
         <v>208</v>
       </c>
     </row>

--- a/Parbaudes_lapu_versijas_jautajumi.xlsx
+++ b/Parbaudes_lapu_versijas_jautajumi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\vpp-cfla\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506534F9-9A42-40BD-88EC-ACB1C0D9F703}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B92364-5B68-4143-AC10-DC06AAAC8A74}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="212">
   <si>
     <t>09.12.2019.</t>
   </si>
@@ -655,6 +655,12 @@
   </si>
   <si>
     <t>7</t>
+  </si>
+  <si>
+    <t>37.43</t>
+  </si>
+  <si>
+    <t>69</t>
   </si>
 </sst>
 </file>
@@ -1069,6 +1075,9 @@
       <c r="D8" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -1083,6 +1092,9 @@
       <c r="D9" s="2" t="s">
         <v>209</v>
       </c>
+      <c r="E9" s="2" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -1097,6 +1109,9 @@
       <c r="D10" s="2">
         <v>8</v>
       </c>
+      <c r="E10" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -1111,6 +1126,9 @@
       <c r="D11" s="2">
         <v>8.1</v>
       </c>
+      <c r="E11" s="2">
+        <v>8.1</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -1125,6 +1143,9 @@
       <c r="D12" s="2">
         <v>8.1999999999999993</v>
       </c>
+      <c r="E12" s="2">
+        <v>8.1999999999999993</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -1139,6 +1160,9 @@
       <c r="D13" s="2">
         <v>8.3000000000000007</v>
       </c>
+      <c r="E13" s="2">
+        <v>8.3000000000000007</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1153,6 +1177,9 @@
       <c r="D14" s="2">
         <v>9</v>
       </c>
+      <c r="E14" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1167,6 +1194,9 @@
       <c r="D15" s="2">
         <v>10</v>
       </c>
+      <c r="E15" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1181,8 +1211,11 @@
       <c r="D16" s="2">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>13</v>
       </c>
@@ -1195,8 +1228,11 @@
       <c r="D17" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>14</v>
       </c>
@@ -1206,8 +1242,11 @@
       <c r="D18" s="2">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>15</v>
       </c>
@@ -1217,8 +1256,11 @@
       <c r="D19" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>16</v>
       </c>
@@ -1228,8 +1270,11 @@
       <c r="D20" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>17</v>
       </c>
@@ -1239,8 +1284,11 @@
       <c r="D21" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>18</v>
       </c>
@@ -1250,8 +1298,11 @@
       <c r="D22" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>19</v>
       </c>
@@ -1261,8 +1312,11 @@
       <c r="D23" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>20</v>
       </c>
@@ -1272,8 +1326,11 @@
       <c r="D24" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>21</v>
       </c>
@@ -1286,8 +1343,11 @@
       <c r="D25" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>22</v>
       </c>
@@ -1300,8 +1360,11 @@
       <c r="D26" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>23</v>
       </c>
@@ -1314,8 +1377,11 @@
       <c r="D27" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>24</v>
       </c>
@@ -1328,8 +1394,11 @@
       <c r="D28" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>25</v>
       </c>
@@ -1342,8 +1411,11 @@
       <c r="D29" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>26</v>
       </c>
@@ -1356,8 +1428,11 @@
       <c r="D30" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>27</v>
       </c>
@@ -1370,8 +1445,11 @@
       <c r="D31" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>28</v>
       </c>
@@ -1384,8 +1462,11 @@
       <c r="D32" s="2" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E32" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>29</v>
       </c>
@@ -1398,8 +1479,11 @@
       <c r="D33" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E33" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>30</v>
       </c>
@@ -1412,8 +1496,11 @@
       <c r="D34" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>31</v>
       </c>
@@ -1426,8 +1513,11 @@
       <c r="D35" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E35" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>32</v>
       </c>
@@ -1440,8 +1530,11 @@
       <c r="D36" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E36" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>33</v>
       </c>
@@ -1454,8 +1547,11 @@
       <c r="D37" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E37" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>34</v>
       </c>
@@ -1468,8 +1564,11 @@
       <c r="D38" s="2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E38" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>35</v>
       </c>
@@ -1482,8 +1581,11 @@
       <c r="D39" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E39" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>35.1</v>
       </c>
@@ -1496,8 +1598,11 @@
       <c r="D40" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E40" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>35.200000000000003</v>
       </c>
@@ -1510,8 +1615,11 @@
       <c r="D41" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E41" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>35.299999999999997</v>
       </c>
@@ -1524,8 +1632,11 @@
       <c r="D42" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E42" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>35.4</v>
       </c>
@@ -1538,8 +1649,11 @@
       <c r="D43" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E43" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>35.5</v>
       </c>
@@ -1552,8 +1666,11 @@
       <c r="D44" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E44" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>35.6</v>
       </c>
@@ -1566,8 +1683,11 @@
       <c r="D45" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E45" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>35.700000000000003</v>
       </c>
@@ -1580,8 +1700,11 @@
       <c r="D46" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E46" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>35.799999999999997</v>
       </c>
@@ -1594,8 +1717,11 @@
       <c r="D47" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E47" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>36</v>
       </c>
@@ -1608,8 +1734,11 @@
       <c r="D48" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>37</v>
       </c>
@@ -1622,8 +1751,11 @@
       <c r="D49" s="2" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E49" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>37.1</v>
       </c>
@@ -1636,8 +1768,11 @@
       <c r="D50" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>37.200000000000003</v>
       </c>
@@ -1650,8 +1785,11 @@
       <c r="D51" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>37.299999999999997</v>
       </c>
@@ -1664,8 +1802,11 @@
       <c r="D52" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E52" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>37.4</v>
       </c>
@@ -1678,8 +1819,11 @@
       <c r="D53" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E53" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>37.5</v>
       </c>
@@ -1692,8 +1836,11 @@
       <c r="D54" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E54" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>37.6</v>
       </c>
@@ -1706,8 +1853,11 @@
       <c r="D55" s="2" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E55" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>37.700000000000003</v>
       </c>
@@ -1720,8 +1870,11 @@
       <c r="D56" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E56" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>37.799999999999997</v>
       </c>
@@ -1734,8 +1887,11 @@
       <c r="D57" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E57" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>37.9</v>
       </c>
@@ -1748,8 +1904,11 @@
       <c r="D58" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E58" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>7</v>
       </c>
@@ -1762,8 +1921,11 @@
       <c r="D59" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E59" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>37.11</v>
       </c>
@@ -1776,8 +1938,11 @@
       <c r="D60" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E60" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>37.119999999999997</v>
       </c>
@@ -1790,8 +1955,11 @@
       <c r="D61" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E61" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>37.130000000000003</v>
       </c>
@@ -1804,8 +1972,11 @@
       <c r="D62" s="2" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E62" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>38</v>
       </c>
@@ -1818,8 +1989,11 @@
       <c r="D63" s="2" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E63" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>38.1</v>
       </c>
@@ -1832,8 +2006,11 @@
       <c r="D64" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E64" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>38.200000000000003</v>
       </c>
@@ -1846,8 +2023,11 @@
       <c r="D65" s="2" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E65" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>38.299999999999997</v>
       </c>
@@ -1860,8 +2040,11 @@
       <c r="D66" s="2" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E66" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>38.4</v>
       </c>
@@ -1874,8 +2057,11 @@
       <c r="D67" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E67" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>38.5</v>
       </c>
@@ -1888,8 +2074,11 @@
       <c r="D68" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E68" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>38.6</v>
       </c>
@@ -1902,8 +2091,11 @@
       <c r="D69" s="2" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E69" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>38.700000000000003</v>
       </c>
@@ -1916,8 +2108,11 @@
       <c r="D70" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E70" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>38.799999999999997</v>
       </c>
@@ -1930,8 +2125,11 @@
       <c r="D71" s="2" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E71" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>38.9</v>
       </c>
@@ -1944,8 +2142,11 @@
       <c r="D72" s="2" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E72" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>39</v>
       </c>
@@ -1958,8 +2159,11 @@
       <c r="D73" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E73" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>39.1</v>
       </c>
@@ -1972,8 +2176,11 @@
       <c r="D74" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E74" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>39.200000000000003</v>
       </c>
@@ -1986,8 +2193,11 @@
       <c r="D75" s="2" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E75" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>39.299999999999997</v>
       </c>
@@ -2000,8 +2210,11 @@
       <c r="D76" s="2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E76" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>39.4</v>
       </c>
@@ -2014,8 +2227,11 @@
       <c r="D77" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E77" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>39.5</v>
       </c>
@@ -2028,8 +2244,11 @@
       <c r="D78" s="2" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E78" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>39.6</v>
       </c>
@@ -2042,8 +2261,11 @@
       <c r="D79" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E79" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>39.700000000000003</v>
       </c>
@@ -2056,8 +2278,11 @@
       <c r="D80" s="2" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E80" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>39.799999999999997</v>
       </c>
@@ -2070,8 +2295,11 @@
       <c r="D81" s="2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E81" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>39.9</v>
       </c>
@@ -2084,8 +2312,11 @@
       <c r="D82" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E82" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>8</v>
       </c>
@@ -2098,8 +2329,11 @@
       <c r="D83" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E83" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>39.11</v>
       </c>
@@ -2112,8 +2346,11 @@
       <c r="D84" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E84" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>39.119999999999997</v>
       </c>
@@ -2126,8 +2363,11 @@
       <c r="D85" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E85" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>39.130000000000003</v>
       </c>
@@ -2140,8 +2380,11 @@
       <c r="D86" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E86" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>39.14</v>
       </c>
@@ -2154,8 +2397,11 @@
       <c r="D87" s="2" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E87" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>39.15</v>
       </c>
@@ -2168,8 +2414,11 @@
       <c r="D88" s="2" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E88" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>39.159999999999997</v>
       </c>
@@ -2182,8 +2431,11 @@
       <c r="D89" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E89" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>39.17</v>
       </c>
@@ -2196,8 +2448,11 @@
       <c r="D90" s="2" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E90" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>39.18</v>
       </c>
@@ -2210,8 +2465,11 @@
       <c r="D91" s="2" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E91" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>39.19</v>
       </c>
@@ -2224,8 +2482,11 @@
       <c r="D92" s="2" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E92" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>9</v>
       </c>
@@ -2238,8 +2499,11 @@
       <c r="D93" s="2" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E93" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>39.21</v>
       </c>
@@ -2252,8 +2516,11 @@
       <c r="D94" s="2" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E94" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>39.22</v>
       </c>
@@ -2266,8 +2533,11 @@
       <c r="D95" s="2" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E95" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>39.229999999999997</v>
       </c>
@@ -2280,8 +2550,11 @@
       <c r="D96" s="2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E96" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>39.24</v>
       </c>
@@ -2294,8 +2567,11 @@
       <c r="D97" s="2" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E97" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>39.25</v>
       </c>
@@ -2308,8 +2584,11 @@
       <c r="D98" s="2" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E98" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>39.26</v>
       </c>
@@ -2322,8 +2601,11 @@
       <c r="D99" s="2" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E99" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>39.270000000000003</v>
       </c>
@@ -2336,8 +2618,11 @@
       <c r="D100" s="2" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E100" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>39.28</v>
       </c>
@@ -2350,8 +2635,11 @@
       <c r="D101" s="2" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E101" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>39.29</v>
       </c>
@@ -2364,8 +2652,11 @@
       <c r="D102" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E102" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>11</v>
       </c>
@@ -2378,8 +2669,11 @@
       <c r="D103" s="2" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E103" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>39.31</v>
       </c>
@@ -2392,8 +2686,11 @@
       <c r="D104" s="2" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E104" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>39.32</v>
       </c>
@@ -2406,8 +2703,11 @@
       <c r="D105" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E105" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>39.33</v>
       </c>
@@ -2420,8 +2720,11 @@
       <c r="D106" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E106" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>39.340000000000003</v>
       </c>
@@ -2434,8 +2737,11 @@
       <c r="D107" s="2" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E107" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>39.35</v>
       </c>
@@ -2448,8 +2754,11 @@
       <c r="D108" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E108" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>39.36</v>
       </c>
@@ -2462,8 +2771,11 @@
       <c r="D109" s="2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E109" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>39.369999999999997</v>
       </c>
@@ -2476,8 +2788,11 @@
       <c r="D110" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E110" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>39.380000000000003</v>
       </c>
@@ -2490,8 +2805,11 @@
       <c r="D111" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E111" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>39.39</v>
       </c>
@@ -2504,8 +2822,11 @@
       <c r="D112" s="2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E112" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>22</v>
       </c>
@@ -2518,8 +2839,11 @@
       <c r="D113" s="2" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E113" s="1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>40</v>
       </c>
@@ -2532,8 +2856,11 @@
       <c r="D114" s="2" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E114" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>40.1</v>
       </c>
@@ -2546,8 +2873,11 @@
       <c r="D115" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E115" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>40.200000000000003</v>
       </c>
@@ -2560,8 +2890,11 @@
       <c r="D116" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E116" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>40.299999999999997</v>
       </c>
@@ -2574,8 +2907,11 @@
       <c r="D117" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E117" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>40.4</v>
       </c>
@@ -2588,8 +2924,11 @@
       <c r="D118" s="2" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E118" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>40.5</v>
       </c>
@@ -2602,8 +2941,11 @@
       <c r="D119" s="2" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E119" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>40.6</v>
       </c>
@@ -2616,8 +2958,11 @@
       <c r="D120" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E120" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>40.700000000000003</v>
       </c>
@@ -2630,8 +2975,11 @@
       <c r="D121" s="2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E121" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>40.799999999999997</v>
       </c>
@@ -2644,8 +2992,11 @@
       <c r="D122" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E122" s="2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>40.9</v>
       </c>
@@ -2658,8 +3009,11 @@
       <c r="D123" s="2" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E123" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>54</v>
       </c>
@@ -2672,8 +3026,11 @@
       <c r="D124" s="2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E124" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>40.11</v>
       </c>
@@ -2686,8 +3043,11 @@
       <c r="D125" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E125" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>40.119999999999997</v>
       </c>
@@ -2700,8 +3060,11 @@
       <c r="D126" s="2" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E126" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>41</v>
       </c>
@@ -2714,8 +3077,11 @@
       <c r="D127" s="2" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E127" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>42</v>
       </c>
@@ -2728,8 +3094,11 @@
       <c r="D128" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E128" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>43</v>
       </c>
@@ -2742,8 +3111,11 @@
       <c r="D129" s="2" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E129" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>44</v>
       </c>
@@ -2756,8 +3128,11 @@
       <c r="D130" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E130" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>45</v>
       </c>
@@ -2770,8 +3145,11 @@
       <c r="D131" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E131" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>46</v>
       </c>
@@ -2784,8 +3162,11 @@
       <c r="D132" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E132" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>47</v>
       </c>
@@ -2798,8 +3179,11 @@
       <c r="D133" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E133" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>48</v>
       </c>
@@ -2812,8 +3196,11 @@
       <c r="D134" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E134" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>49</v>
       </c>
@@ -2826,8 +3213,11 @@
       <c r="D135" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E135" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>50</v>
       </c>
@@ -2840,8 +3230,11 @@
       <c r="D136" s="2" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E136" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>51</v>
       </c>
@@ -2854,8 +3247,11 @@
       <c r="D137" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E137" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>51.1</v>
       </c>
@@ -2868,8 +3264,11 @@
       <c r="D138" s="2" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E138" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>51.2</v>
       </c>
@@ -2882,8 +3281,11 @@
       <c r="D139" s="2" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E139" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>51.3</v>
       </c>
@@ -2896,8 +3298,11 @@
       <c r="D140" s="2" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E140" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>51.4</v>
       </c>
@@ -2910,8 +3315,11 @@
       <c r="D141" s="2" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E141" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>52</v>
       </c>
@@ -2924,8 +3332,11 @@
       <c r="D142" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E142" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>53</v>
       </c>
@@ -2938,8 +3349,11 @@
       <c r="D143" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E143" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>54</v>
       </c>
@@ -2952,8 +3366,11 @@
       <c r="D144" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E144" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>55</v>
       </c>
@@ -2966,8 +3383,11 @@
       <c r="D145" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E145" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>56</v>
       </c>
@@ -2980,8 +3400,11 @@
       <c r="D146" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E146" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>57</v>
       </c>
@@ -2994,8 +3417,11 @@
       <c r="D147" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E147" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>58</v>
       </c>
@@ -3008,8 +3434,11 @@
       <c r="D148" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E148" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>59</v>
       </c>
@@ -3022,8 +3451,11 @@
       <c r="D149" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E149" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>60</v>
       </c>
@@ -3036,8 +3468,11 @@
       <c r="D150" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E150" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>61</v>
       </c>
@@ -3050,8 +3485,11 @@
       <c r="D151" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E151" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>62</v>
       </c>
@@ -3064,8 +3502,11 @@
       <c r="D152" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E152" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>63</v>
       </c>
@@ -3078,8 +3519,11 @@
       <c r="D153" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E153" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>64</v>
       </c>
@@ -3092,8 +3536,11 @@
       <c r="D154" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E154" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>65</v>
       </c>
@@ -3106,8 +3553,11 @@
       <c r="D155" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E155" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>66</v>
       </c>
@@ -3120,8 +3570,11 @@
       <c r="D156" s="2" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E156" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>67</v>
       </c>
@@ -3134,8 +3587,11 @@
       <c r="D157" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E157" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>68</v>
       </c>
@@ -3147,6 +3603,9 @@
       </c>
       <c r="D158" s="2" t="s">
         <v>208</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/Parbaudes_lapu_versijas_jautajumi.xlsx
+++ b/Parbaudes_lapu_versijas_jautajumi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\vpp-cfla\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B92364-5B68-4143-AC10-DC06AAAC8A74}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E1CC0C-6ECD-401C-8C1B-65FF051609B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="277">
   <si>
     <t>09.12.2019.</t>
   </si>
@@ -661,6 +661,201 @@
   </si>
   <si>
     <t>69</t>
+  </si>
+  <si>
+    <t>30.8</t>
+  </si>
+  <si>
+    <t>30.1</t>
+  </si>
+  <si>
+    <t>30.2</t>
+  </si>
+  <si>
+    <t>30.3</t>
+  </si>
+  <si>
+    <t>30.4</t>
+  </si>
+  <si>
+    <t>30.5</t>
+  </si>
+  <si>
+    <t>30.6</t>
+  </si>
+  <si>
+    <t>30.7</t>
+  </si>
+  <si>
+    <t>32.14</t>
+  </si>
+  <si>
+    <t>32.1</t>
+  </si>
+  <si>
+    <t>32.2</t>
+  </si>
+  <si>
+    <t>32.3</t>
+  </si>
+  <si>
+    <t>32.4</t>
+  </si>
+  <si>
+    <t>32.5</t>
+  </si>
+  <si>
+    <t>32.8</t>
+  </si>
+  <si>
+    <t>32.10</t>
+  </si>
+  <si>
+    <t>32.11</t>
+  </si>
+  <si>
+    <t>32.6</t>
+  </si>
+  <si>
+    <t>32.7</t>
+  </si>
+  <si>
+    <t>32.9</t>
+  </si>
+  <si>
+    <t>32.12</t>
+  </si>
+  <si>
+    <t>34.1</t>
+  </si>
+  <si>
+    <t>34.2</t>
+  </si>
+  <si>
+    <t>34.3</t>
+  </si>
+  <si>
+    <t>34.4</t>
+  </si>
+  <si>
+    <t>34.43</t>
+  </si>
+  <si>
+    <t>34.6</t>
+  </si>
+  <si>
+    <t>34.7</t>
+  </si>
+  <si>
+    <t>34.8</t>
+  </si>
+  <si>
+    <t>34.9</t>
+  </si>
+  <si>
+    <t>34.10</t>
+  </si>
+  <si>
+    <t>34.11</t>
+  </si>
+  <si>
+    <t>34.12</t>
+  </si>
+  <si>
+    <t>34.13</t>
+  </si>
+  <si>
+    <t>34.14</t>
+  </si>
+  <si>
+    <t>34.15</t>
+  </si>
+  <si>
+    <t>34.16</t>
+  </si>
+  <si>
+    <t>34.17</t>
+  </si>
+  <si>
+    <t>34.18</t>
+  </si>
+  <si>
+    <t>34.19</t>
+  </si>
+  <si>
+    <t>34.20</t>
+  </si>
+  <si>
+    <t>34.21</t>
+  </si>
+  <si>
+    <t>34.22</t>
+  </si>
+  <si>
+    <t>34.23</t>
+  </si>
+  <si>
+    <t>34.24</t>
+  </si>
+  <si>
+    <t>34.25</t>
+  </si>
+  <si>
+    <t>34.26</t>
+  </si>
+  <si>
+    <t>34.27</t>
+  </si>
+  <si>
+    <t>34.28</t>
+  </si>
+  <si>
+    <t>34.29</t>
+  </si>
+  <si>
+    <t>34.30</t>
+  </si>
+  <si>
+    <t>34.31</t>
+  </si>
+  <si>
+    <t>34.32</t>
+  </si>
+  <si>
+    <t>34.33</t>
+  </si>
+  <si>
+    <t>34.34</t>
+  </si>
+  <si>
+    <t>34.35</t>
+  </si>
+  <si>
+    <t>34.36</t>
+  </si>
+  <si>
+    <t>34.37</t>
+  </si>
+  <si>
+    <t>34.38</t>
+  </si>
+  <si>
+    <t>34.39</t>
+  </si>
+  <si>
+    <t>47.2</t>
+  </si>
+  <si>
+    <t>47.3</t>
+  </si>
+  <si>
+    <t>47.5</t>
+  </si>
+  <si>
+    <t>67</t>
+  </si>
+  <si>
+    <t>47.4</t>
   </si>
 </sst>
 </file>
@@ -993,10 +1188,10 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="13" style="2" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="8.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1078,6 +1273,9 @@
       <c r="E8" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="F8" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
@@ -1095,6 +1293,9 @@
       <c r="E9" s="2" t="s">
         <v>209</v>
       </c>
+      <c r="F9" s="2" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -1112,6 +1313,9 @@
       <c r="E10" s="2">
         <v>8</v>
       </c>
+      <c r="F10" s="2">
+        <v>8</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
@@ -1129,6 +1333,9 @@
       <c r="E11" s="2">
         <v>8.1</v>
       </c>
+      <c r="F11" s="2">
+        <v>8.1</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -1146,6 +1353,9 @@
       <c r="E12" s="2">
         <v>8.1999999999999993</v>
       </c>
+      <c r="F12" s="2">
+        <v>8.1999999999999993</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
@@ -1163,6 +1373,9 @@
       <c r="E13" s="2">
         <v>8.3000000000000007</v>
       </c>
+      <c r="F13" s="2">
+        <v>8.3000000000000007</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1180,6 +1393,9 @@
       <c r="E14" s="2">
         <v>9</v>
       </c>
+      <c r="F14" s="2">
+        <v>9</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
@@ -1197,6 +1413,9 @@
       <c r="E15" s="2">
         <v>10</v>
       </c>
+      <c r="F15" s="2">
+        <v>10</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1214,8 +1433,11 @@
       <c r="E16" s="2">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>13</v>
       </c>
@@ -1231,8 +1453,11 @@
       <c r="E17" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>14</v>
       </c>
@@ -1245,8 +1470,11 @@
       <c r="E18" s="2">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>15</v>
       </c>
@@ -1259,8 +1487,11 @@
       <c r="E19" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>16</v>
       </c>
@@ -1273,8 +1504,11 @@
       <c r="E20" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>17</v>
       </c>
@@ -1287,8 +1521,11 @@
       <c r="E21" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>18</v>
       </c>
@@ -1301,8 +1538,11 @@
       <c r="E22" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>19</v>
       </c>
@@ -1315,8 +1555,11 @@
       <c r="E23" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>20</v>
       </c>
@@ -1329,8 +1572,11 @@
       <c r="E24" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>21</v>
       </c>
@@ -1346,8 +1592,11 @@
       <c r="E25" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>22</v>
       </c>
@@ -1363,8 +1612,11 @@
       <c r="E26" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>23</v>
       </c>
@@ -1380,8 +1632,11 @@
       <c r="E27" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>24</v>
       </c>
@@ -1397,8 +1652,11 @@
       <c r="E28" s="2" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>25</v>
       </c>
@@ -1414,8 +1672,11 @@
       <c r="E29" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>26</v>
       </c>
@@ -1431,8 +1692,11 @@
       <c r="E30" s="2" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>27</v>
       </c>
@@ -1448,8 +1712,11 @@
       <c r="E31" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>28</v>
       </c>
@@ -1465,8 +1732,11 @@
       <c r="E32" s="2" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>29</v>
       </c>
@@ -1482,8 +1752,11 @@
       <c r="E33" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>30</v>
       </c>
@@ -1499,8 +1772,11 @@
       <c r="E34" s="2" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>31</v>
       </c>
@@ -1516,8 +1792,11 @@
       <c r="E35" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>32</v>
       </c>
@@ -1533,8 +1812,11 @@
       <c r="E36" s="2" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>33</v>
       </c>
@@ -1550,8 +1832,11 @@
       <c r="E37" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>34</v>
       </c>
@@ -1567,8 +1852,11 @@
       <c r="E38" s="2" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>35</v>
       </c>
@@ -1584,8 +1872,11 @@
       <c r="E39" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>35.1</v>
       </c>
@@ -1601,8 +1892,11 @@
       <c r="E40" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>35.200000000000003</v>
       </c>
@@ -1618,8 +1912,11 @@
       <c r="E41" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>35.299999999999997</v>
       </c>
@@ -1635,8 +1932,11 @@
       <c r="E42" s="2" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>35.4</v>
       </c>
@@ -1652,8 +1952,11 @@
       <c r="E43" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>35.5</v>
       </c>
@@ -1669,8 +1972,11 @@
       <c r="E44" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>35.6</v>
       </c>
@@ -1686,8 +1992,11 @@
       <c r="E45" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>35.700000000000003</v>
       </c>
@@ -1703,8 +2012,11 @@
       <c r="E46" s="2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>35.799999999999997</v>
       </c>
@@ -1720,8 +2032,11 @@
       <c r="E47" s="2" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>36</v>
       </c>
@@ -1737,8 +2052,11 @@
       <c r="E48" s="2" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F48" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>37</v>
       </c>
@@ -1754,8 +2072,11 @@
       <c r="E49" s="2" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>37.1</v>
       </c>
@@ -1771,8 +2092,11 @@
       <c r="E50" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>37.200000000000003</v>
       </c>
@@ -1788,8 +2112,11 @@
       <c r="E51" s="2" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F51" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>37.299999999999997</v>
       </c>
@@ -1805,8 +2132,11 @@
       <c r="E52" s="2" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F52" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>37.4</v>
       </c>
@@ -1822,8 +2152,11 @@
       <c r="E53" s="2" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F53" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>37.5</v>
       </c>
@@ -1839,8 +2172,11 @@
       <c r="E54" s="2" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>37.6</v>
       </c>
@@ -1856,8 +2192,11 @@
       <c r="E55" s="2" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>37.700000000000003</v>
       </c>
@@ -1873,8 +2212,11 @@
       <c r="E56" s="2" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>37.799999999999997</v>
       </c>
@@ -1890,8 +2232,11 @@
       <c r="E57" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>37.9</v>
       </c>
@@ -1907,8 +2252,11 @@
       <c r="E58" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>7</v>
       </c>
@@ -1924,8 +2272,11 @@
       <c r="E59" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F59" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>37.11</v>
       </c>
@@ -1941,8 +2292,11 @@
       <c r="E60" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F60" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>37.119999999999997</v>
       </c>
@@ -1958,8 +2312,11 @@
       <c r="E61" s="2" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>37.130000000000003</v>
       </c>
@@ -1975,8 +2332,11 @@
       <c r="E62" s="2" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>38</v>
       </c>
@@ -1992,8 +2352,11 @@
       <c r="E63" s="2" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>38.1</v>
       </c>
@@ -2009,8 +2372,11 @@
       <c r="E64" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F64" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>38.200000000000003</v>
       </c>
@@ -2026,8 +2392,11 @@
       <c r="E65" s="2" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F65" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>38.299999999999997</v>
       </c>
@@ -2043,8 +2412,11 @@
       <c r="E66" s="2" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F66" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>38.4</v>
       </c>
@@ -2060,8 +2432,11 @@
       <c r="E67" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>38.5</v>
       </c>
@@ -2077,8 +2452,11 @@
       <c r="E68" s="2" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F68" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>38.6</v>
       </c>
@@ -2094,8 +2472,11 @@
       <c r="E69" s="2" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F69" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>38.700000000000003</v>
       </c>
@@ -2111,8 +2492,11 @@
       <c r="E70" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F70" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>38.799999999999997</v>
       </c>
@@ -2128,8 +2512,11 @@
       <c r="E71" s="2" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F71" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>38.9</v>
       </c>
@@ -2145,8 +2532,11 @@
       <c r="E72" s="2" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F72" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>39</v>
       </c>
@@ -2162,8 +2552,11 @@
       <c r="E73" s="2" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F73" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>39.1</v>
       </c>
@@ -2179,8 +2572,11 @@
       <c r="E74" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F74" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>39.200000000000003</v>
       </c>
@@ -2196,8 +2592,11 @@
       <c r="E75" s="2" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F75" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>39.299999999999997</v>
       </c>
@@ -2213,8 +2612,11 @@
       <c r="E76" s="2" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F76" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>39.4</v>
       </c>
@@ -2230,8 +2632,11 @@
       <c r="E77" s="2" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F77" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>39.5</v>
       </c>
@@ -2247,8 +2652,11 @@
       <c r="E78" s="2" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>39.6</v>
       </c>
@@ -2264,8 +2672,11 @@
       <c r="E79" s="2" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F79" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>39.700000000000003</v>
       </c>
@@ -2281,8 +2692,11 @@
       <c r="E80" s="2" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F80" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>39.799999999999997</v>
       </c>
@@ -2298,8 +2712,11 @@
       <c r="E81" s="2" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F81" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>39.9</v>
       </c>
@@ -2315,8 +2732,11 @@
       <c r="E82" s="2" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F82" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>8</v>
       </c>
@@ -2332,8 +2752,11 @@
       <c r="E83" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F83" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>39.11</v>
       </c>
@@ -2349,8 +2772,11 @@
       <c r="E84" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F84" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>39.119999999999997</v>
       </c>
@@ -2366,8 +2792,11 @@
       <c r="E85" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F85" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>39.130000000000003</v>
       </c>
@@ -2383,8 +2812,11 @@
       <c r="E86" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F86" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>39.14</v>
       </c>
@@ -2400,8 +2832,11 @@
       <c r="E87" s="2" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F87" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>39.15</v>
       </c>
@@ -2417,8 +2852,11 @@
       <c r="E88" s="2" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F88" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>39.159999999999997</v>
       </c>
@@ -2434,8 +2872,11 @@
       <c r="E89" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F89" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>39.17</v>
       </c>
@@ -2451,8 +2892,11 @@
       <c r="E90" s="2" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F90" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>39.18</v>
       </c>
@@ -2468,8 +2912,11 @@
       <c r="E91" s="2" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F91" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>39.19</v>
       </c>
@@ -2485,8 +2932,11 @@
       <c r="E92" s="2" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F92" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>9</v>
       </c>
@@ -2502,8 +2952,11 @@
       <c r="E93" s="2" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F93" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>39.21</v>
       </c>
@@ -2519,8 +2972,11 @@
       <c r="E94" s="2" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F94" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>39.22</v>
       </c>
@@ -2536,8 +2992,11 @@
       <c r="E95" s="2" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F95" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>39.229999999999997</v>
       </c>
@@ -2553,8 +3012,11 @@
       <c r="E96" s="2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F96" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>39.24</v>
       </c>
@@ -2570,8 +3032,11 @@
       <c r="E97" s="2" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F97" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>39.25</v>
       </c>
@@ -2587,8 +3052,11 @@
       <c r="E98" s="2" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F98" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>39.26</v>
       </c>
@@ -2604,8 +3072,11 @@
       <c r="E99" s="2" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F99" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>39.270000000000003</v>
       </c>
@@ -2621,8 +3092,11 @@
       <c r="E100" s="2" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F100" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>39.28</v>
       </c>
@@ -2638,8 +3112,11 @@
       <c r="E101" s="2" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F101" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>39.29</v>
       </c>
@@ -2655,8 +3132,11 @@
       <c r="E102" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F102" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>11</v>
       </c>
@@ -2672,8 +3152,11 @@
       <c r="E103" s="2" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F103" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>39.31</v>
       </c>
@@ -2689,8 +3172,11 @@
       <c r="E104" s="2" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F104" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>39.32</v>
       </c>
@@ -2706,8 +3192,11 @@
       <c r="E105" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F105" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>39.33</v>
       </c>
@@ -2723,8 +3212,11 @@
       <c r="E106" s="2" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F106" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>39.340000000000003</v>
       </c>
@@ -2740,8 +3232,11 @@
       <c r="E107" s="2" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F107" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>39.35</v>
       </c>
@@ -2757,8 +3252,11 @@
       <c r="E108" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F108" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>39.36</v>
       </c>
@@ -2774,8 +3272,11 @@
       <c r="E109" s="2" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F109" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>39.369999999999997</v>
       </c>
@@ -2791,8 +3292,11 @@
       <c r="E110" s="2" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F110" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>39.380000000000003</v>
       </c>
@@ -2808,8 +3312,11 @@
       <c r="E111" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F111" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>39.39</v>
       </c>
@@ -2825,8 +3332,11 @@
       <c r="E112" s="2" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F112" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>22</v>
       </c>
@@ -2842,8 +3352,11 @@
       <c r="E113" s="1" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F113" s="1" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>40</v>
       </c>
@@ -2859,8 +3372,11 @@
       <c r="E114" s="2" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F114" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>40.1</v>
       </c>
@@ -2876,8 +3392,11 @@
       <c r="E115" s="2" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F115" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>40.200000000000003</v>
       </c>
@@ -2893,8 +3412,11 @@
       <c r="E116" s="2" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F116" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>40.299999999999997</v>
       </c>
@@ -2910,8 +3432,11 @@
       <c r="E117" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F117" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>40.4</v>
       </c>
@@ -2927,8 +3452,11 @@
       <c r="E118" s="2" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F118" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>40.5</v>
       </c>
@@ -2944,8 +3472,11 @@
       <c r="E119" s="2" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F119" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>40.6</v>
       </c>
@@ -2961,8 +3492,11 @@
       <c r="E120" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F120" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>40.700000000000003</v>
       </c>
@@ -2978,8 +3512,11 @@
       <c r="E121" s="2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F121" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>40.799999999999997</v>
       </c>
@@ -2995,8 +3532,11 @@
       <c r="E122" s="2" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F122" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>40.9</v>
       </c>
@@ -3012,8 +3552,11 @@
       <c r="E123" s="2" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F123" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>54</v>
       </c>
@@ -3029,8 +3572,11 @@
       <c r="E124" s="2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F124" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>40.11</v>
       </c>
@@ -3046,8 +3592,11 @@
       <c r="E125" s="2" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F125" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>40.119999999999997</v>
       </c>
@@ -3063,8 +3612,11 @@
       <c r="E126" s="2" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F126" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>41</v>
       </c>
@@ -3080,8 +3632,11 @@
       <c r="E127" s="2" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F127" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>42</v>
       </c>
@@ -3097,8 +3652,11 @@
       <c r="E128" s="2" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F128" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>43</v>
       </c>
@@ -3114,8 +3672,11 @@
       <c r="E129" s="2" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F129" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>44</v>
       </c>
@@ -3131,8 +3692,11 @@
       <c r="E130" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F130" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>45</v>
       </c>
@@ -3148,8 +3712,11 @@
       <c r="E131" s="2" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F131" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>46</v>
       </c>
@@ -3165,8 +3732,11 @@
       <c r="E132" s="2" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F132" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>47</v>
       </c>
@@ -3182,8 +3752,11 @@
       <c r="E133" s="2" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F133" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>48</v>
       </c>
@@ -3199,8 +3772,11 @@
       <c r="E134" s="2" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F134" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>49</v>
       </c>
@@ -3216,8 +3792,11 @@
       <c r="E135" s="2" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F135" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>50</v>
       </c>
@@ -3233,8 +3812,11 @@
       <c r="E136" s="2" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F136" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>51</v>
       </c>
@@ -3250,8 +3832,11 @@
       <c r="E137" s="2" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F137" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>51.1</v>
       </c>
@@ -3267,8 +3852,11 @@
       <c r="E138" s="2" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F138" s="1" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>51.2</v>
       </c>
@@ -3284,8 +3872,11 @@
       <c r="E139" s="2" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F139" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>51.3</v>
       </c>
@@ -3301,8 +3892,11 @@
       <c r="E140" s="2" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F140" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>51.4</v>
       </c>
@@ -3318,8 +3912,11 @@
       <c r="E141" s="2" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F141" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>52</v>
       </c>
@@ -3335,8 +3932,11 @@
       <c r="E142" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F142" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>53</v>
       </c>
@@ -3352,8 +3952,11 @@
       <c r="E143" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F143" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>54</v>
       </c>
@@ -3369,8 +3972,11 @@
       <c r="E144" s="2" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F144" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>55</v>
       </c>
@@ -3386,8 +3992,11 @@
       <c r="E145" s="2" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F145" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>56</v>
       </c>
@@ -3403,8 +4012,11 @@
       <c r="E146" s="2" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F146" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>57</v>
       </c>
@@ -3420,8 +4032,11 @@
       <c r="E147" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F147" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>58</v>
       </c>
@@ -3437,8 +4052,11 @@
       <c r="E148" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F148" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>59</v>
       </c>
@@ -3454,8 +4072,11 @@
       <c r="E149" s="2" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F149" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>60</v>
       </c>
@@ -3471,8 +4092,11 @@
       <c r="E150" s="2" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F150" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>61</v>
       </c>
@@ -3488,8 +4112,11 @@
       <c r="E151" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F151" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>62</v>
       </c>
@@ -3505,8 +4132,11 @@
       <c r="E152" s="2" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F152" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>63</v>
       </c>
@@ -3522,8 +4152,11 @@
       <c r="E153" s="2" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F153" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>64</v>
       </c>
@@ -3539,8 +4172,11 @@
       <c r="E154" s="2" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F154" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>65</v>
       </c>
@@ -3556,8 +4192,11 @@
       <c r="E155" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F155" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>66</v>
       </c>
@@ -3573,8 +4212,11 @@
       <c r="E156" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F156" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>67</v>
       </c>
@@ -3590,8 +4232,11 @@
       <c r="E157" s="2" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F157" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>68</v>
       </c>
@@ -3606,6 +4251,9 @@
       </c>
       <c r="E158" s="1" t="s">
         <v>211</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>275</v>
       </c>
     </row>
   </sheetData>

--- a/Parbaudes_lapu_versijas_jautajumi.xlsx
+++ b/Parbaudes_lapu_versijas_jautajumi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\vpp-cfla\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23E1CC0C-6ECD-401C-8C1B-65FF051609B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28164E40-875A-4C66-A0D4-5DD361F9B035}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="328">
   <si>
     <t>09.12.2019.</t>
   </si>
@@ -147,9 +147,6 @@
     <t>42.35</t>
   </si>
   <si>
-    <t>42.24</t>
-  </si>
-  <si>
     <t>42.33</t>
   </si>
   <si>
@@ -856,6 +853,162 @@
   </si>
   <si>
     <t>47.4</t>
+  </si>
+  <si>
+    <t>29.1</t>
+  </si>
+  <si>
+    <t>29.2</t>
+  </si>
+  <si>
+    <t>29.4</t>
+  </si>
+  <si>
+    <t>29.5</t>
+  </si>
+  <si>
+    <t>31.1</t>
+  </si>
+  <si>
+    <t>31.2</t>
+  </si>
+  <si>
+    <t>31.5</t>
+  </si>
+  <si>
+    <t>31.6</t>
+  </si>
+  <si>
+    <t>31.7</t>
+  </si>
+  <si>
+    <t>31.8</t>
+  </si>
+  <si>
+    <t>31.9</t>
+  </si>
+  <si>
+    <t>03.04.2019.-PND</t>
+  </si>
+  <si>
+    <t>33.10</t>
+  </si>
+  <si>
+    <t>33.11</t>
+  </si>
+  <si>
+    <t>33.12</t>
+  </si>
+  <si>
+    <t>33.13</t>
+  </si>
+  <si>
+    <t>33.14</t>
+  </si>
+  <si>
+    <t>34.5</t>
+  </si>
+  <si>
+    <t>35.25</t>
+  </si>
+  <si>
+    <t>35.14</t>
+  </si>
+  <si>
+    <t>35.15</t>
+  </si>
+  <si>
+    <t>35.16</t>
+  </si>
+  <si>
+    <t>35.17</t>
+  </si>
+  <si>
+    <t>35.18</t>
+  </si>
+  <si>
+    <t>35.19</t>
+  </si>
+  <si>
+    <t>35.20</t>
+  </si>
+  <si>
+    <t>35.21</t>
+  </si>
+  <si>
+    <t>35.23</t>
+  </si>
+  <si>
+    <t>35.37</t>
+  </si>
+  <si>
+    <t>35.36</t>
+  </si>
+  <si>
+    <t>35.26</t>
+  </si>
+  <si>
+    <t>35.27</t>
+  </si>
+  <si>
+    <t>35.28</t>
+  </si>
+  <si>
+    <t>35.29</t>
+  </si>
+  <si>
+    <t>35.30</t>
+  </si>
+  <si>
+    <t>35.31</t>
+  </si>
+  <si>
+    <t>35.32</t>
+  </si>
+  <si>
+    <t>35.33</t>
+  </si>
+  <si>
+    <t>35.34</t>
+  </si>
+  <si>
+    <t>35.35</t>
+  </si>
+  <si>
+    <t>42.34</t>
+  </si>
+  <si>
+    <t>35.38</t>
+  </si>
+  <si>
+    <t>35.41</t>
+  </si>
+  <si>
+    <t>35.42</t>
+  </si>
+  <si>
+    <t>35.43</t>
+  </si>
+  <si>
+    <t>35.45</t>
+  </si>
+  <si>
+    <t>35.46</t>
+  </si>
+  <si>
+    <t>35.47</t>
+  </si>
+  <si>
+    <t>36.10</t>
+  </si>
+  <si>
+    <t>36.11</t>
+  </si>
+  <si>
+    <t>36.12</t>
+  </si>
+  <si>
+    <t>37.4.1</t>
   </si>
 </sst>
 </file>
@@ -1184,88 +1337,104 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="8.140625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="1.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="2">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C4" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C6" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C7" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2">
         <v>8</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>6</v>
+      <c r="C8" s="2">
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>6</v>
@@ -1276,8 +1445,11 @@
       <c r="F8" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1285,19 +1457,22 @@
         <v>9</v>
       </c>
       <c r="C9" s="2">
+        <v>9</v>
+      </c>
+      <c r="D9" s="2">
         <v>7</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="E9" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>208</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1305,7 +1480,7 @@
         <v>10</v>
       </c>
       <c r="C10" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2">
         <v>8</v>
@@ -1316,8 +1491,11 @@
       <c r="F10" s="2">
         <v>8</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>9.1</v>
       </c>
@@ -1325,7 +1503,7 @@
         <v>10.1</v>
       </c>
       <c r="C11" s="2">
-        <v>8.1</v>
+        <v>10.1</v>
       </c>
       <c r="D11" s="2">
         <v>8.1</v>
@@ -1336,8 +1514,11 @@
       <c r="F11" s="2">
         <v>8.1</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="2">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>9.1999999999999993</v>
       </c>
@@ -1345,7 +1526,7 @@
         <v>10.199999999999999</v>
       </c>
       <c r="C12" s="2">
-        <v>8.1999999999999993</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="D12" s="2">
         <v>8.1999999999999993</v>
@@ -1356,8 +1537,11 @@
       <c r="F12" s="2">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="2">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>9.3000000000000007</v>
       </c>
@@ -1365,7 +1549,7 @@
         <v>10.3</v>
       </c>
       <c r="C13" s="2">
-        <v>8.3000000000000007</v>
+        <v>10.3</v>
       </c>
       <c r="D13" s="2">
         <v>8.3000000000000007</v>
@@ -1376,8 +1560,11 @@
       <c r="F13" s="2">
         <v>8.3000000000000007</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="2">
+        <v>8.3000000000000007</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>10</v>
       </c>
@@ -1385,7 +1572,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D14" s="2">
         <v>9</v>
@@ -1396,8 +1583,11 @@
       <c r="F14" s="2">
         <v>9</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>11</v>
       </c>
@@ -1405,7 +1595,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D15" s="2">
         <v>10</v>
@@ -1416,8 +1606,11 @@
       <c r="F15" s="2">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>12</v>
       </c>
@@ -1425,7 +1618,7 @@
         <v>13</v>
       </c>
       <c r="C16" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2">
         <v>11</v>
@@ -1436,16 +1629,19 @@
       <c r="F16" s="2">
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="2">
-        <v>12</v>
+      <c r="C17" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="D17" s="2">
         <v>12</v>
@@ -1456,14 +1652,14 @@
       <c r="F17" s="2">
         <v>12</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>14</v>
       </c>
-      <c r="C18" s="2">
-        <v>13</v>
-      </c>
       <c r="D18" s="2">
         <v>13</v>
       </c>
@@ -1473,65 +1669,65 @@
       <c r="F18" s="2">
         <v>13</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>15</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="D19" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>16</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>95</v>
-      </c>
       <c r="D20" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>17</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="D21" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>18</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="D22" s="2" t="s">
         <v>6</v>
       </c>
@@ -1541,382 +1737,436 @@
       <c r="F22" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>19</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>20</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>21</v>
       </c>
       <c r="B25" s="2">
         <v>22</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>99</v>
+      <c r="C25" s="2">
+        <v>22</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>22</v>
       </c>
       <c r="B26" s="2">
         <v>23</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>100</v>
+      <c r="C26" s="2">
+        <v>23</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>23</v>
       </c>
       <c r="B27" s="2">
         <v>24</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>101</v>
+      <c r="C27" s="2">
+        <v>24</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>24</v>
       </c>
       <c r="B28" s="2">
         <v>25</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>102</v>
+      <c r="C28" s="2">
+        <v>25</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>25</v>
       </c>
       <c r="B29" s="2">
         <v>26</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>103</v>
+      <c r="C29" s="2">
+        <v>26</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>26</v>
       </c>
       <c r="B30" s="2">
         <v>27</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>104</v>
+      <c r="C30" s="2">
+        <v>27</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>27</v>
       </c>
       <c r="B31" s="2">
         <v>28</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>105</v>
+      <c r="C31" s="2">
+        <v>28</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>104</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>28</v>
       </c>
       <c r="B32" s="2">
         <v>29</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>106</v>
+      <c r="C32" s="2">
+        <v>29</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>29</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C33" s="2">
         <v>30</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="D33" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>30</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C34" s="2">
         <v>31</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="D34" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>31</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C35" s="2">
         <v>33</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>109</v>
-      </c>
       <c r="D35" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>32</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C36" s="2">
         <v>34</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="D36" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F36" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>33</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="2">
         <v>36</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="D37" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>34</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C38" s="2">
         <v>37</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="D38" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>35</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="2">
         <v>38</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="D39" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>35.1</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C40" s="2">
         <v>38.1</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="D40" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>35.200000000000003</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C41" s="2">
         <v>38.200000000000003</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="D41" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>35.299999999999997</v>
       </c>
@@ -1924,379 +2174,436 @@
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>116</v>
+        <v>6</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>35.4</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C43" s="2">
         <v>38.5</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="D43" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>35.5</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>92</v>
+        <v>283</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>35.6</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C45" s="2">
         <v>38.700000000000003</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="D45" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>35.700000000000003</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C46" s="2">
         <v>38.799999999999997</v>
       </c>
-      <c r="C46" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="D46" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>35.799999999999997</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C47" s="2">
         <v>38.9</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="D47" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>36</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="2">
         <v>39</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="D48" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>37</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C49" s="2">
         <v>40</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="D49" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>37.1</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C50" s="2">
         <v>40.1</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>124</v>
-      </c>
       <c r="D50" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>37.200000000000003</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="2">
         <v>40.200000000000003</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="D51" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>37.299999999999997</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C52" s="2">
         <v>40.299999999999997</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="D52" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>37.4</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C53" s="2">
         <v>40.4</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="D53" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>37.5</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C54" s="2">
         <v>40.5</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>128</v>
-      </c>
       <c r="D54" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>37.6</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="2">
         <v>40.6</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="D55" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>37.700000000000003</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" s="2">
         <v>40.700000000000003</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="D56" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>37.799999999999997</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>54</v>
+        <v>288</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>131</v>
+        <v>53</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>37.9</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C58" s="2">
         <v>40.11</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="D58" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C59" s="2">
         <v>40.119999999999997</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="D59" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>37.11</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C60" s="2">
         <v>40.130000000000003</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="D60" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>37.119999999999997</v>
       </c>
@@ -2304,159 +2611,183 @@
         <v>6</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>135</v>
+        <v>6</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>37.130000000000003</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C62" s="2">
         <v>40.14</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="D62" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>38</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C63" s="2">
         <v>41</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="D63" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>38.1</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C64" s="2">
         <v>41.1</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="D64" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>38.200000000000003</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C65" s="2">
         <v>41.2</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="D65" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>38.299999999999997</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C66" s="2">
         <v>41.3</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="D66" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>38.4</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C67" s="2">
         <v>41.4</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="D67" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F67" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>38.5</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C68" s="2">
         <v>41.5</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="D68" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>38.6</v>
       </c>
@@ -2464,287 +2795,329 @@
         <v>6</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>143</v>
+        <v>6</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>38.700000000000003</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C70" s="2">
         <v>41.8</v>
       </c>
-      <c r="C70" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="D70" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>38.799999999999997</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C71" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="D71" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>38.9</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C72" s="2">
         <v>41.11</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="D72" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>39</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="D73" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>39.1</v>
       </c>
       <c r="B74" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="D74" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>39.200000000000003</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="D75" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>39.299999999999997</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="D76" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>39.4</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="D77" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>39.5</v>
       </c>
       <c r="B78" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C78" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="D78" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F78" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G78" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>39.6</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="D79" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>39.700000000000003</v>
       </c>
       <c r="B80" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="D80" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>39.799999999999997</v>
       </c>
       <c r="B81" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="D81" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>39.9</v>
       </c>
       <c r="B82" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="D82" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B83" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C83" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>7</v>
@@ -2753,590 +3126,680 @@
         <v>7</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>39.11</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C84" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="D84" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>39.119999999999997</v>
       </c>
       <c r="B85" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="D85" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>39.130000000000003</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="D86" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>39.14</v>
       </c>
       <c r="B87" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="D87" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>39.15</v>
       </c>
       <c r="B88" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="D88" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>39.159999999999997</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C89" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="D89" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>39.17</v>
       </c>
       <c r="B90" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C90" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="D90" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>39.18</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="D91" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>39.19</v>
       </c>
       <c r="B92" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="D92" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="D93" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>39.21</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D94" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>39.22</v>
       </c>
       <c r="B95" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C95" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="D95" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>39.229999999999997</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="D96" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>39.24</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C97" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="D97" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>39.25</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="D98" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>39.26</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>43</v>
+        <v>311</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>172</v>
+        <v>42</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>39.270000000000003</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>42</v>
+        <v>312</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>173</v>
+        <v>41</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>39.28</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>41</v>
+        <v>313</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>174</v>
+        <v>40</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>39.29</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>40</v>
+        <v>314</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>175</v>
+        <v>316</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+        <v>174</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B103" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C103" s="2" t="s">
-        <v>176</v>
-      </c>
       <c r="D103" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>39.31</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>44</v>
+        <v>305</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>177</v>
+        <v>43</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>39.32</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>46</v>
+        <v>304</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>178</v>
+        <v>45</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>39.33</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>45</v>
+        <v>317</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>179</v>
+        <v>44</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>39.340000000000003</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>47</v>
+        <v>318</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>39.35</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>48</v>
+        <v>319</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>181</v>
+        <v>47</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>39.36</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>49</v>
+        <v>320</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>182</v>
+        <v>48</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>39.369999999999997</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>50</v>
+        <v>321</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>183</v>
+        <v>49</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>39.380000000000003</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>51</v>
+        <v>322</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>39.39</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>52</v>
+        <v>323</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>185</v>
+        <v>51</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>22</v>
       </c>
@@ -3344,299 +3807,344 @@
         <v>6</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>186</v>
+        <v>6</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>210</v>
+        <v>185</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+        <v>209</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>40</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>187</v>
+        <v>52</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>40.1</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>188</v>
+        <v>54</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>40.200000000000003</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>189</v>
+        <v>55</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>40.299999999999997</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>190</v>
+        <v>56</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>40.4</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>191</v>
+        <v>57</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>40.5</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>192</v>
+        <v>58</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>40.6</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>40.700000000000003</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>193</v>
+        <v>60</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>40.799999999999997</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>194</v>
+        <v>61</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>40.9</v>
       </c>
       <c r="B123" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C123" s="2" t="s">
+      <c r="D124" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D123" s="2" t="s">
+      <c r="E124" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="E123" s="2" t="s">
+      <c r="F124" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="F123" s="2" t="s">
+      <c r="G124" s="2" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>40.11</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>65</v>
+        <v>325</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>197</v>
+        <v>64</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>40.119999999999997</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>66</v>
+        <v>326</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>198</v>
+        <v>65</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+        <v>197</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>41</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>199</v>
+        <v>90</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>42</v>
       </c>
@@ -3644,19 +4152,22 @@
         <v>6</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+        <v>199</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>43</v>
       </c>
@@ -3664,27 +4175,30 @@
         <v>6</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>201</v>
+        <v>6</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>44</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>12</v>
@@ -3693,90 +4207,105 @@
         <v>12</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>45</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>89</v>
+        <v>149</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>53</v>
+        <v>88</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>46</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>88</v>
+        <v>150</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>47</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>87</v>
+        <v>327</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F133" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G133" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>48</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>49</v>
       </c>
@@ -3784,59 +4313,68 @@
         <v>6</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>83</v>
+        <v>6</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>50</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>85</v>
+        <v>186</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>202</v>
+        <v>84</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>51</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C137" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G137" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D137" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>51.1</v>
       </c>
@@ -3844,19 +4382,22 @@
         <v>6</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>203</v>
+        <v>6</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>51.2</v>
       </c>
@@ -3864,19 +4405,22 @@
         <v>6</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>204</v>
+        <v>6</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>51.3</v>
       </c>
@@ -3884,376 +4428,433 @@
         <v>6</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>205</v>
+        <v>6</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>51.4</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>206</v>
+        <v>83</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>52</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>83</v>
+        <v>199</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>53</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>82</v>
+        <v>12</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>81</v>
       </c>
       <c r="D143" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G143" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E143" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>54</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>80</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>55</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>79</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>56</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>78</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>57</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>77</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>58</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>77</v>
+        <v>201</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>76</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>59</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>75</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F149" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G149" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>60</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>75</v>
+        <v>206</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>74</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>61</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>73</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>62</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>72</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>63</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>71</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>64</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>70</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>65</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>69</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>66</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>68</v>
       </c>
       <c r="D156" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G156" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="E156" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F156" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>67</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>67</v>
       </c>
       <c r="D157" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G157" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E157" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="F157" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>68</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>208</v>
+        <v>66</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>275</v>
+        <v>210</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>274</v>
       </c>
     </row>
   </sheetData>
